--- a/artfynd/A 43653-2021 artfynd.xlsx
+++ b/artfynd/A 43653-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43653-2021 artfynd.xlsx
+++ b/artfynd/A 43653-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104158153</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775429.1167395059</v>
+        <v>775429</v>
       </c>
       <c r="R2" t="n">
-        <v>7345268.444500175</v>
+        <v>7345268</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,12 +780,7 @@
         <v>104158159</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775488.8590842334</v>
+        <v>775489</v>
       </c>
       <c r="R3" t="n">
-        <v>7345363.198358957</v>
+        <v>7345363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2022-07-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -912,12 +882,7 @@
         <v>104158157</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775498.0933494861</v>
+        <v>775498</v>
       </c>
       <c r="R4" t="n">
-        <v>7345352.273317817</v>
+        <v>7345352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2022-07-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104158158</v>
+        <v>104158154</v>
       </c>
       <c r="B5" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775492.4422354335</v>
+        <v>775631</v>
       </c>
       <c r="R5" t="n">
-        <v>7345339.077206685</v>
+        <v>7345308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2022-07-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1146,12 +1086,7 @@
         <v>104158156</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775504.8280764739</v>
+        <v>775505</v>
       </c>
       <c r="R6" t="n">
-        <v>7345379.442411274</v>
+        <v>7345379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2022-07-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104158154</v>
+        <v>104158158</v>
       </c>
       <c r="B7" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775630.6599950851</v>
+        <v>775492</v>
       </c>
       <c r="R7" t="n">
-        <v>7345307.728482499</v>
+        <v>7345339</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2022-07-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 43653-2021 artfynd.xlsx
+++ b/artfynd/A 43653-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158153</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158157</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158154</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158156</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158158</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>